--- a/criterios.xlsx
+++ b/criterios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\plataforma-seguimiento-financiero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCA4238-BCCC-434D-88D1-317F4DBD424B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EF5A13-BC47-4DF4-A162-E0DDEEFCB769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D5990060-E24B-4D72-B684-1372D2201E14}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="107">
   <si>
     <t>CA</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Nombre normalizado</t>
   </si>
   <si>
-    <t>Tipo</t>
-  </si>
-  <si>
     <t>fechadelaconsulta</t>
   </si>
   <si>
@@ -343,6 +340,21 @@
   </si>
   <si>
     <t>Importe ejecutado</t>
+  </si>
+  <si>
+    <t>Tipo para individuales</t>
+  </si>
+  <si>
+    <t>Grafico</t>
+  </si>
+  <si>
+    <t>Tipo para versus</t>
+  </si>
+  <si>
+    <t>Gráfico</t>
+  </si>
+  <si>
+    <t>Filtro metrica</t>
   </si>
 </sst>
 </file>
@@ -719,652 +731,759 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{124EE4ED-7B54-470B-9BB7-8A8FE6BB3C39}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="25.44140625" customWidth="1"/>
+    <col min="5" max="5" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
+      <c r="B18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E32" s="2"/>
+      <c r="F32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F33" s="2"/>
+      <c r="G33" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F34" s="2"/>
+      <c r="G34" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
+      <c r="C35" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F35" s="2"/>
+      <c r="G35" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F36" s="2"/>
+      <c r="G36" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
+      <c r="C37" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-      <c r="F37" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F37" s="2"/>
+      <c r="G37" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F38" s="2"/>
+      <c r="G38" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F39" s="2"/>
+      <c r="G39" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F40" s="2"/>
+      <c r="G40" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F41" s="2"/>
+      <c r="G41" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F42" s="2"/>
+      <c r="G42" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F43" s="2"/>
+      <c r="G43" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
+      <c r="C44" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="2"/>
+      <c r="G44" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="2"/>
+      <c r="G45" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>79</v>
       </c>
@@ -1372,35 +1491,38 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="2"/>
+      <c r="G46" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="2"/>
+      <c r="G47" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="2"/>
+      <c r="G48" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>81</v>
       </c>
@@ -1408,32 +1530,22 @@
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="2"/>
+      <c r="G49" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2" t="s">
-        <v>77</v>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/criterios.xlsx
+++ b/criterios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\plataforma-seguimiento-financiero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EF5A13-BC47-4DF4-A162-E0DDEEFCB769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3647B8E-669D-47F5-91CB-06BF0760E8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D5990060-E24B-4D72-B684-1372D2201E14}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="104">
   <si>
     <t>CA</t>
   </si>
@@ -240,24 +240,12 @@
     <t>fuente_financ_agregada</t>
   </si>
   <si>
-    <t>centro_costo</t>
-  </si>
-  <si>
-    <t>nombre_depend</t>
-  </si>
-  <si>
     <t>tipo_tarea</t>
   </si>
   <si>
     <t>nivel_tarea</t>
   </si>
   <si>
-    <t>codigo_tarea</t>
-  </si>
-  <si>
-    <t>nombre_tarea</t>
-  </si>
-  <si>
     <t>valor_depend</t>
   </si>
   <si>
@@ -276,18 +264,12 @@
     <t>Nivel tarea</t>
   </si>
   <si>
-    <t>Nombre tarea</t>
-  </si>
-  <si>
     <t>Valor depend</t>
   </si>
   <si>
     <t>Sec_func</t>
   </si>
   <si>
-    <t>Nombre</t>
-  </si>
-  <si>
     <t>Nro de orden</t>
   </si>
   <si>
@@ -312,12 +294,6 @@
     <t>Fuente de financiamiento agregada</t>
   </si>
   <si>
-    <t>Dependencia</t>
-  </si>
-  <si>
-    <t>Código tarea</t>
-  </si>
-  <si>
     <t>Valor impto soles</t>
   </si>
   <si>
@@ -339,9 +315,6 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>Importe ejecutado</t>
-  </si>
-  <si>
     <t>Tipo para individuales</t>
   </si>
   <si>
@@ -351,10 +324,28 @@
     <t>Tipo para versus</t>
   </si>
   <si>
-    <t>Gráfico</t>
-  </si>
-  <si>
     <t>Filtro metrica</t>
+  </si>
+  <si>
+    <t>Importe ejecutado SIGA</t>
+  </si>
+  <si>
+    <t>centro_costo - nombre_depend</t>
+  </si>
+  <si>
+    <t>codigo_tarea - nombre_tarea</t>
+  </si>
+  <si>
+    <t>clasificador(("."," "),1,2)</t>
+  </si>
+  <si>
+    <t>clasificador(("."," "),3,1)</t>
+  </si>
+  <si>
+    <t>clasificador(("."," "),4,1)</t>
+  </si>
+  <si>
+    <t>clasificador(("."," "),5,1)</t>
   </si>
 </sst>
 </file>
@@ -731,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{124EE4ED-7B54-470B-9BB7-8A8FE6BB3C39}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -747,13 +738,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -762,7 +753,7 @@
         <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -770,10 +761,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
@@ -786,13 +777,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -806,10 +797,10 @@
         <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
@@ -825,10 +816,10 @@
         <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
@@ -844,10 +835,10 @@
         <v>28</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
@@ -863,10 +854,10 @@
         <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
@@ -882,10 +873,10 @@
         <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
@@ -901,10 +892,10 @@
         <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
@@ -923,7 +914,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
@@ -942,7 +933,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -950,7 +941,7 @@
         <v>44</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -961,14 +952,16 @@
         <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -978,10 +971,10 @@
         <v>43</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>10</v>
@@ -999,10 +992,10 @@
         <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>11</v>
@@ -1010,7 +1003,9 @@
       <c r="F14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="2"/>
+      <c r="G14" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
@@ -1040,7 +1035,7 @@
         <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>13</v>
@@ -1048,7 +1043,9 @@
       <c r="F16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
@@ -1065,7 +1062,9 @@
         <v>14</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="G17" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
@@ -1082,7 +1081,9 @@
         <v>15</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
@@ -1095,23 +1096,25 @@
         <v>43</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
@@ -1127,10 +1130,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
@@ -1185,10 +1188,10 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
@@ -1205,7 +1208,7 @@
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
@@ -1232,10 +1235,10 @@
         <v>55</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -1249,10 +1252,10 @@
         <v>54</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -1266,10 +1269,10 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1306,24 +1309,24 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -1336,50 +1339,48 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
+      <c r="C36" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B37" s="2"/>
-      <c r="C37" s="2" t="s">
-        <v>103</v>
-      </c>
+      <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1387,12 +1388,12 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -1400,12 +1401,12 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -1413,12 +1414,12 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -1426,12 +1427,12 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -1439,12 +1440,12 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -1452,17 +1453,15 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B44" s="2"/>
-      <c r="C44" s="2" t="s">
-        <v>105</v>
-      </c>
+      <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -1472,7 +1471,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -1485,7 +1484,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -1493,59 +1492,7 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/criterios.xlsx
+++ b/criterios.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\plataforma-seguimiento-financiero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Otros ordenadores\Mi portátil (1)\Documents\plataforma-seguimiento-financiero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3647B8E-669D-47F5-91CB-06BF0760E8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585BAEC4-B5BE-415C-968F-A9C6DD595E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D5990060-E24B-4D72-B684-1372D2201E14}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D5990060-E24B-4D72-B684-1372D2201E14}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="comparaciones" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="116">
   <si>
     <t>CA</t>
   </si>
@@ -346,6 +347,42 @@
   </si>
   <si>
     <t>clasificador(("."," "),5,1)</t>
+  </si>
+  <si>
+    <t>Agrupador</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Etapa/Texto “desc”</t>
+  </si>
+  <si>
+    <t>Etapa/Texto “inc”</t>
+  </si>
+  <si>
+    <t>Umbral</t>
+  </si>
+  <si>
+    <t>Incluir 0 vs +</t>
+  </si>
+  <si>
+    <t>sí</t>
+  </si>
+  <si>
+    <t>modificación de presupuesto</t>
+  </si>
+  <si>
+    <t>devengado</t>
+  </si>
+  <si>
+    <t>modificación de POI</t>
+  </si>
+  <si>
+    <t>ejecución (órdenes)</t>
   </si>
 </sst>
 </file>
@@ -404,10 +441,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1498,4 +1541,221 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0CAE69B-D255-485A-B4DA-E2EA8918E960}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/criterios.xlsx
+++ b/criterios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Otros ordenadores\Mi portátil (1)\Documents\plataforma-seguimiento-financiero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\plataforma-seguimiento-financiero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585BAEC4-B5BE-415C-968F-A9C6DD595E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589FBEE5-1770-4D31-960E-F1FF82251203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D5990060-E24B-4D72-B684-1372D2201E14}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D5990060-E24B-4D72-B684-1372D2201E14}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="116">
   <si>
     <t>CA</t>
   </si>
@@ -469,9 +469,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -509,7 +509,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -615,7 +615,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -757,7 +757,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -959,7 +959,9 @@
       <c r="C10" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
